--- a/セリフ編集/キャラ個人別/プロフィール.xlsx
+++ b/セリフ編集/キャラ個人別/プロフィール.xlsx
@@ -1750,19 +1750,19 @@
           <t xml:space="preserve">37</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr" s="6">
+      <c r="E37" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">白銀麗子</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr" s="6">
+      <c r="F37" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">丁寧</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G37" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="3">
@@ -2422,19 +2422,19 @@
           <t xml:space="preserve">53</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr" s="5">
+      <c r="E53" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">小森さなえ</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr" s="5">
+      <c r="F53" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G53" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H53" t="inlineStr" s="3">
@@ -2968,19 +2968,19 @@
           <t xml:space="preserve">66</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr" s="5">
+      <c r="E66" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">長谷川レオナ</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr" s="5">
+      <c r="F66" t="inlineStr" s="10">
         <is>
           <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="G66" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="H66" t="inlineStr" s="3">
@@ -3220,19 +3220,19 @@
           <t xml:space="preserve">72</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr" s="5">
+      <c r="E72" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">穴澤ほのか</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F72" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="H72" t="inlineStr" s="3">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F75" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="9">
@@ -3724,19 +3724,19 @@
           <t xml:space="preserve">84</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr" s="6">
+      <c r="E84" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">南谷杏</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr" s="6">
+      <c r="F84" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+      <c r="G84" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="H84" t="inlineStr" s="3">
@@ -4690,19 +4690,19 @@
           <t xml:space="preserve">107</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr" s="5">
+      <c r="E107" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">松岡綾乃</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F107" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="H107" t="inlineStr" s="3">
@@ -5278,19 +5278,19 @@
           <t xml:space="preserve">121</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr" s="5">
+      <c r="E121" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">山本理香</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+      <c r="F121" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="H121" t="inlineStr" s="3">
